--- a/Data/EC/NIT-8904801916.xlsx
+++ b/Data/EC/NIT-8904801916.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51F775A0-3438-4441-A31A-3BBD1C0B9FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F5F546F-EDE9-4707-BE4C-6FF43B9A21E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{04FB8ABB-C60A-41E4-B87E-7226E46703D5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{AE76B976-50AA-4503-9E42-28D7B6A3F62B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="138">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,334 +71,352 @@
     <t>GILBERTO LUIS BORNACHERA YEPEZ</t>
   </si>
   <si>
+    <t>2602</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
+  </si>
+  <si>
+    <t>2511</t>
+  </si>
+  <si>
+    <t>2510</t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>2508</t>
+  </si>
+  <si>
+    <t>2507</t>
+  </si>
+  <si>
+    <t>2506</t>
+  </si>
+  <si>
+    <t>2505</t>
+  </si>
+  <si>
+    <t>2504</t>
+  </si>
+  <si>
+    <t>2503</t>
+  </si>
+  <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
-  </si>
-  <si>
-    <t>2503</t>
-  </si>
-  <si>
-    <t>2504</t>
-  </si>
-  <si>
-    <t>2505</t>
-  </si>
-  <si>
-    <t>2506</t>
-  </si>
-  <si>
-    <t>2507</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -497,9 +515,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -512,7 +528,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -712,23 +730,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -756,10 +774,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -797,22 +815,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1561B808-7A95-4B5C-CC09-8653099BE878}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B578294-ADBE-B261-3EF3-D90226B28A98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -834,7 +852,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1163,27 +1181,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAAA771-5C52-42E5-A06E-4CE752CA9EB0}">
-  <dimension ref="B2:J131"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{897533A3-17D1-441D-AA3C-295461FFA8C2}">
+  <dimension ref="B2:J137"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1192,7 +1210,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1203,7 +1221,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1214,7 +1232,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1225,10 +1243,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1241,8 +1259,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1257,15 +1275,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>3265556</v>
+        <v>3453050</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1273,27 +1291,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F13" s="5">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1313,16 +1331,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1336,7 +1354,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1345,7 +1363,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1359,7 +1377,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1368,7 +1386,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1382,7 +1400,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1391,7 +1409,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1405,7 +1423,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1414,7 +1432,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1446,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1437,7 +1455,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1451,7 +1469,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1460,7 +1478,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1474,7 +1492,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1483,7 +1501,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1506,7 +1524,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1529,7 +1547,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1543,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1552,7 +1570,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1566,7 +1584,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1575,7 +1593,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1589,7 +1607,7 @@
         <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1598,7 +1616,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1612,7 +1630,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1621,7 +1639,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1635,7 +1653,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1644,7 +1662,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1658,7 +1676,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1667,7 +1685,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1681,7 +1699,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1690,7 +1708,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1722,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1713,7 +1731,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1727,7 +1745,7 @@
         <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1736,7 +1754,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1768,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1759,7 +1777,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1773,7 +1791,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1782,7 +1800,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1796,7 +1814,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1805,7 +1823,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1819,7 +1837,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1828,7 +1846,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1842,7 +1860,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1851,7 +1869,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1865,7 +1883,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1874,7 +1892,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1906,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1897,7 +1915,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1911,7 +1929,7 @@
         <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>24640</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1920,7 +1938,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1943,7 +1961,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1966,7 +1984,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +2007,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2030,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2035,7 +2053,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2058,7 +2076,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2081,7 +2099,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2104,7 +2122,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2127,7 +2145,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2150,7 +2168,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2173,7 +2191,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2196,7 +2214,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2219,7 +2237,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2242,7 +2260,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2265,7 +2283,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2288,7 +2306,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2311,7 +2329,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2334,7 +2352,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2357,7 +2375,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2380,7 +2398,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2403,7 +2421,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2426,7 +2444,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2467,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2472,7 +2490,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2495,7 +2513,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2518,7 +2536,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2541,7 +2559,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2564,7 +2582,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2587,7 +2605,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2628,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2633,7 +2651,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2674,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2679,7 +2697,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2702,7 +2720,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2725,7 +2743,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +2766,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2789,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2794,7 +2812,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2817,7 +2835,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2840,7 +2858,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2863,7 +2881,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2904,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2909,7 +2927,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2932,7 +2950,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2955,7 +2973,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2978,7 +2996,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -3001,7 +3019,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -3024,7 +3042,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3047,7 +3065,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3070,7 +3088,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3093,7 +3111,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3116,7 +3134,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +3157,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3180,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3185,7 +3203,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3208,7 +3226,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3231,7 +3249,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3254,7 +3272,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3277,7 +3295,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3300,7 +3318,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3323,7 +3341,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3346,7 +3364,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3369,7 +3387,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3392,7 +3410,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3406,7 +3424,7 @@
         <v>101</v>
       </c>
       <c r="F106" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G106" s="18">
         <v>781242</v>
@@ -3415,7 +3433,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3429,7 +3447,7 @@
         <v>102</v>
       </c>
       <c r="F107" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G107" s="18">
         <v>781242</v>
@@ -3438,7 +3456,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3452,7 +3470,7 @@
         <v>103</v>
       </c>
       <c r="F108" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G108" s="18">
         <v>781242</v>
@@ -3461,7 +3479,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3475,7 +3493,7 @@
         <v>104</v>
       </c>
       <c r="F109" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G109" s="18">
         <v>781242</v>
@@ -3484,7 +3502,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3498,7 +3516,7 @@
         <v>105</v>
       </c>
       <c r="F110" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G110" s="18">
         <v>781242</v>
@@ -3507,7 +3525,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3521,7 +3539,7 @@
         <v>106</v>
       </c>
       <c r="F111" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G111" s="18">
         <v>781242</v>
@@ -3530,7 +3548,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3544,7 +3562,7 @@
         <v>107</v>
       </c>
       <c r="F112" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G112" s="18">
         <v>781242</v>
@@ -3553,7 +3571,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3567,7 +3585,7 @@
         <v>108</v>
       </c>
       <c r="F113" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G113" s="18">
         <v>781242</v>
@@ -3576,7 +3594,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3590,7 +3608,7 @@
         <v>109</v>
       </c>
       <c r="F114" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G114" s="18">
         <v>781242</v>
@@ -3599,7 +3617,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3613,7 +3631,7 @@
         <v>110</v>
       </c>
       <c r="F115" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G115" s="18">
         <v>781242</v>
@@ -3622,7 +3640,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3636,7 +3654,7 @@
         <v>111</v>
       </c>
       <c r="F116" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G116" s="18">
         <v>781242</v>
@@ -3645,7 +3663,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3659,7 +3677,7 @@
         <v>112</v>
       </c>
       <c r="F117" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G117" s="18">
         <v>781242</v>
@@ -3668,7 +3686,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3682,7 +3700,7 @@
         <v>113</v>
       </c>
       <c r="F118" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G118" s="18">
         <v>781242</v>
@@ -3691,7 +3709,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3705,7 +3723,7 @@
         <v>114</v>
       </c>
       <c r="F119" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G119" s="18">
         <v>781242</v>
@@ -3714,7 +3732,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3728,7 +3746,7 @@
         <v>115</v>
       </c>
       <c r="F120" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G120" s="18">
         <v>781242</v>
@@ -3737,7 +3755,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3751,7 +3769,7 @@
         <v>116</v>
       </c>
       <c r="F121" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G121" s="18">
         <v>781242</v>
@@ -3760,7 +3778,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3774,7 +3792,7 @@
         <v>117</v>
       </c>
       <c r="F122" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G122" s="18">
         <v>781242</v>
@@ -3783,7 +3801,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3797,7 +3815,7 @@
         <v>118</v>
       </c>
       <c r="F123" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G123" s="18">
         <v>781242</v>
@@ -3806,7 +3824,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3820,7 +3838,7 @@
         <v>119</v>
       </c>
       <c r="F124" s="18">
-        <v>31249</v>
+        <v>24640</v>
       </c>
       <c r="G124" s="18">
         <v>781242</v>
@@ -3829,57 +3847,195 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B125" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D125" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="22" t="s">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B125" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F125" s="24">
-        <v>31249</v>
-      </c>
-      <c r="G125" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-      <c r="J125" s="26"/>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B130" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C130" s="32"/>
-      <c r="H130" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B131" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C131" s="32"/>
-      <c r="H131" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="F125" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G125" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="20"/>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F126" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G126" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="20"/>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F127" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G127" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="20"/>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B128" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F128" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G128" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="20"/>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B129" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F129" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G129" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="20"/>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F130" s="18">
+        <v>24640</v>
+      </c>
+      <c r="G130" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="20"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F131" s="24">
+        <v>24640</v>
+      </c>
+      <c r="G131" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H131" s="25"/>
+      <c r="I131" s="25"/>
+      <c r="J131" s="26"/>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B136" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C136" s="32"/>
+      <c r="H136" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B137" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C137" s="32"/>
+      <c r="H137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I137" s="1"/>
+      <c r="J137" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="H130:J130"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="H137:J137"/>
+    <mergeCell ref="H136:J136"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
